--- a/商業（しょうぎょう）.xlsx
+++ b/商業（しょうぎょう）.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\苗欣奕的东西\折跃\Japanese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE69942-7B0C-4BCB-A232-622A7C893871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6EA8A79-1B56-40A9-89DF-463A619CEAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="基礎「きそ」" sheetId="1" r:id="rId1"/>
     <sheet name="業務（ぎょうむ）" sheetId="2" r:id="rId2"/>
     <sheet name="買い物（かいもの）" sheetId="4" r:id="rId3"/>
     <sheet name="分析（ぶんせき）" sheetId="3" r:id="rId4"/>
